--- a/SPEC MyBook Pro 103.2.xlsx
+++ b/SPEC MyBook Pro 103.2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Downloads\Spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Desktop\axioo_b2g\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6E2FFB-97E3-4CED-9A2B-256CC93D1F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DD41B5-B4F5-40CB-B29E-C42645A1C8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -202,44 +202,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -255,23 +220,58 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -361,122 +361,119 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,369 +783,361 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="17" customWidth="1"/>
-    <col min="2" max="2" width="88.33203125" style="17" customWidth="1"/>
-    <col min="3" max="5" width="8.88671875" style="17"/>
-    <col min="6" max="6" width="21.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="17"/>
-    <col min="10" max="10" width="21.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="74.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="17"/>
+    <col min="1" max="1" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="8.88671875" style="2"/>
+    <col min="6" max="6" width="21.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" style="2"/>
+    <col min="10" max="10" width="21.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="74.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="12"/>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20"/>
+      <c r="A3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="20"/>
+      <c r="A4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="13"/>
+      <c r="A6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
+      <c r="A7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="12"/>
+      <c r="A9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="15"/>
+      <c r="A10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="8"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="29"/>
-      <c r="B13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="12"/>
+      <c r="A13" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="12"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="29"/>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="12"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="23"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="14"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="29"/>
-      <c r="B17" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="12"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="29"/>
-      <c r="B18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="19"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="29"/>
-      <c r="B19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="12"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="29"/>
-      <c r="B20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="19"/>
+      <c r="A20" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="26"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="32"/>
-      <c r="B22" s="30" t="s">
-        <v>32</v>
+      <c r="A22" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="F22" s="19"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="12"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="12"/>
+      <c r="A24" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>37</v>
+      <c r="A25" s="20"/>
+      <c r="B25" s="27" t="s">
+        <v>38</v>
       </c>
       <c r="F25" s="19"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="29"/>
-      <c r="B26" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="12"/>
+      <c r="A26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
+      <c r="A27" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="15"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="3" t="s">
+      <c r="A28" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B28" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="15"/>
-    </row>
-    <row r="30" spans="1:7" ht="15">
-      <c r="A30" s="3" t="s">
+      <c r="F28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" ht="13.2">
+      <c r="A29" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B29" s="29" t="s">
         <v>46</v>
       </c>
     </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A31" s="31"/>
+      <c r="B31" s="31"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="31"/>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="16"/>
-      <c r="B33" s="16"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="21"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="25"/>
-      <c r="B34" s="8"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="21"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="25"/>
-      <c r="B35" s="8"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="32"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="26"/>
-      <c r="B36" s="1"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="31"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
+      <c r="A37" s="31"/>
+      <c r="B37" s="31"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="31"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="16"/>
-      <c r="B39" s="16"/>
+      <c r="A39" s="31"/>
+      <c r="B39" s="31"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="16"/>
-      <c r="B40" s="16"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="34"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="34"/>
-      <c r="B41" s="35"/>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="36"/>
-      <c r="B42" s="16"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="F13:F18"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F17"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="A20:A21"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1387,21 +1376,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D50C5B06-61E5-46A2-81C4-43CCDD918A8D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE8BAC0-C575-4EA2-89D7-8A2A3A262846}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
-    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1426,9 +1414,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE8BAC0-C575-4EA2-89D7-8A2A3A262846}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D50C5B06-61E5-46A2-81C4-43CCDD918A8D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
+    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>